--- a/DS Assignment Instructions.xlsx
+++ b/DS Assignment Instructions.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2671367-4344-4391-8400-A9B6706D9051}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aman2\OneDrive\Desktop\Celebal-Excellence-Internship-Weekly-Assignment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4A6E55-648F-43ED-885D-1BB6500BD1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -184,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,14 +561,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="76.28515625" customWidth="1"/>
-    <col min="3" max="3" width="63.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="2" max="2" width="76.33203125" customWidth="1"/>
+    <col min="3" max="3" width="63.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,7 +579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="213">
+    <row r="2" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -587,7 +590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="305.25">
+    <row r="3" spans="1:3" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -598,7 +601,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="259.5">
+    <row r="4" spans="1:3" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -609,7 +612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="229.5">
+    <row r="5" spans="1:3" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -620,7 +623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="229.5">
+    <row r="6" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -631,7 +634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="198">
+    <row r="7" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -642,7 +645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="244.5">
+    <row r="8" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -653,7 +656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="229.5">
+    <row r="9" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
